--- a/downloads/korea-1944-tables.xlsx
+++ b/downloads/korea-1944-tables.xlsx
@@ -600,7 +600,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>朝鮮事情 1944 (Chōsen jijō, 昭和十九年版) — tables</t>
+          <t>朝鮮事情 1944 — tables</t>
         </is>
       </c>
     </row>
